--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113756</v>
+        <v>125113758</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454675</v>
+        <v>454729</v>
       </c>
       <c r="R2" t="n">
-        <v>6991059</v>
+        <v>6991137</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113751</v>
+        <v>125113757</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454727</v>
+        <v>454714</v>
       </c>
       <c r="R3" t="n">
-        <v>6991007</v>
+        <v>6991134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113757</v>
+        <v>125113749</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454714</v>
+        <v>454596</v>
       </c>
       <c r="R4" t="n">
-        <v>6991134</v>
+        <v>6991073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113755</v>
+        <v>125113750</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454683</v>
+        <v>454597</v>
       </c>
       <c r="R5" t="n">
-        <v>6991038</v>
+        <v>6991074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113700</v>
+        <v>125113747</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454596</v>
+        <v>454528</v>
       </c>
       <c r="R6" t="n">
-        <v>6991038</v>
+        <v>6990951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113758</v>
+        <v>125113760</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454729</v>
+        <v>454751</v>
       </c>
       <c r="R7" t="n">
-        <v>6991137</v>
+        <v>6991130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113750</v>
+        <v>125113751</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454597</v>
+        <v>454727</v>
       </c>
       <c r="R8" t="n">
-        <v>6991074</v>
+        <v>6991007</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113754</v>
+        <v>125113753</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454717</v>
+        <v>454759</v>
       </c>
       <c r="R9" t="n">
-        <v>6991021</v>
+        <v>6990995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113748</v>
+        <v>125113754</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454594</v>
+        <v>454717</v>
       </c>
       <c r="R10" t="n">
-        <v>6991074</v>
+        <v>6991021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113786</v>
+        <v>125113748</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454563</v>
+        <v>454594</v>
       </c>
       <c r="R11" t="n">
-        <v>6991041</v>
+        <v>6991074</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113749</v>
+        <v>125113755</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454596</v>
+        <v>454683</v>
       </c>
       <c r="R12" t="n">
-        <v>6991073</v>
+        <v>6991038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113753</v>
+        <v>125113786</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454759</v>
+        <v>454563</v>
       </c>
       <c r="R13" t="n">
-        <v>6990995</v>
+        <v>6991041</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113747</v>
+        <v>125113700</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454528</v>
+        <v>454596</v>
       </c>
       <c r="R14" t="n">
-        <v>6990951</v>
+        <v>6991038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113760</v>
+        <v>125113756</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454751</v>
+        <v>454675</v>
       </c>
       <c r="R15" t="n">
-        <v>6991130</v>
+        <v>6991059</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113758</v>
+        <v>125113786</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454729</v>
+        <v>454563</v>
       </c>
       <c r="R2" t="n">
-        <v>6991137</v>
+        <v>6991041</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113757</v>
+        <v>125113754</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454714</v>
+        <v>454717</v>
       </c>
       <c r="R3" t="n">
-        <v>6991134</v>
+        <v>6991021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113749</v>
+        <v>125113760</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454596</v>
+        <v>454751</v>
       </c>
       <c r="R4" t="n">
-        <v>6991073</v>
+        <v>6991130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113750</v>
+        <v>125113751</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454597</v>
+        <v>454727</v>
       </c>
       <c r="R5" t="n">
-        <v>6991074</v>
+        <v>6991007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113747</v>
+        <v>125113750</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454528</v>
+        <v>454597</v>
       </c>
       <c r="R6" t="n">
-        <v>6990951</v>
+        <v>6991074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113760</v>
+        <v>125113748</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454751</v>
+        <v>454594</v>
       </c>
       <c r="R7" t="n">
-        <v>6991130</v>
+        <v>6991074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113751</v>
+        <v>125113747</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454727</v>
+        <v>454528</v>
       </c>
       <c r="R8" t="n">
-        <v>6991007</v>
+        <v>6990951</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113753</v>
+        <v>125113700</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454759</v>
+        <v>454596</v>
       </c>
       <c r="R9" t="n">
-        <v>6990995</v>
+        <v>6991038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113754</v>
+        <v>125113753</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1571,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454717</v>
+        <v>454759</v>
       </c>
       <c r="R10" t="n">
-        <v>6991021</v>
+        <v>6990995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113748</v>
+        <v>125113756</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1678,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454594</v>
+        <v>454675</v>
       </c>
       <c r="R11" t="n">
-        <v>6991074</v>
+        <v>6991059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113755</v>
+        <v>125113758</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1785,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454683</v>
+        <v>454729</v>
       </c>
       <c r="R12" t="n">
-        <v>6991038</v>
+        <v>6991137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113786</v>
+        <v>125113757</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454563</v>
+        <v>454714</v>
       </c>
       <c r="R13" t="n">
-        <v>6991041</v>
+        <v>6991134</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113700</v>
+        <v>125113755</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,7 +1989,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454596</v>
+        <v>454683</v>
       </c>
       <c r="R14" t="n">
         <v>6991038</v>
@@ -2030,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113756</v>
+        <v>125113749</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454675</v>
+        <v>454596</v>
       </c>
       <c r="R15" t="n">
-        <v>6991059</v>
+        <v>6991073</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113786</v>
+        <v>125113755</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454563</v>
+        <v>454683</v>
       </c>
       <c r="R2" t="n">
-        <v>6991041</v>
+        <v>6991038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113754</v>
+        <v>125113757</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454717</v>
+        <v>454714</v>
       </c>
       <c r="R3" t="n">
-        <v>6991021</v>
+        <v>6991134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113760</v>
+        <v>125113750</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454751</v>
+        <v>454597</v>
       </c>
       <c r="R4" t="n">
-        <v>6991130</v>
+        <v>6991074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113751</v>
+        <v>125113786</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454727</v>
+        <v>454563</v>
       </c>
       <c r="R5" t="n">
-        <v>6991007</v>
+        <v>6991041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113750</v>
+        <v>125113753</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454597</v>
+        <v>454759</v>
       </c>
       <c r="R6" t="n">
-        <v>6991074</v>
+        <v>6990995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113748</v>
+        <v>125113749</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454594</v>
+        <v>454596</v>
       </c>
       <c r="R7" t="n">
-        <v>6991074</v>
+        <v>6991073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113747</v>
+        <v>125113754</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454528</v>
+        <v>454717</v>
       </c>
       <c r="R8" t="n">
-        <v>6990951</v>
+        <v>6991021</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113700</v>
+        <v>125113751</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454596</v>
+        <v>454727</v>
       </c>
       <c r="R9" t="n">
-        <v>6991038</v>
+        <v>6991007</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113753</v>
+        <v>125113756</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454759</v>
+        <v>454675</v>
       </c>
       <c r="R10" t="n">
-        <v>6990995</v>
+        <v>6991059</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113756</v>
+        <v>125113700</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454675</v>
+        <v>454596</v>
       </c>
       <c r="R11" t="n">
-        <v>6991059</v>
+        <v>6991038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113757</v>
+        <v>125113748</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454714</v>
+        <v>454594</v>
       </c>
       <c r="R13" t="n">
-        <v>6991134</v>
+        <v>6991074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113755</v>
+        <v>125113760</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454683</v>
+        <v>454751</v>
       </c>
       <c r="R14" t="n">
-        <v>6991038</v>
+        <v>6991130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113749</v>
+        <v>125113747</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454596</v>
+        <v>454528</v>
       </c>
       <c r="R15" t="n">
-        <v>6991073</v>
+        <v>6990951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113755</v>
+        <v>125113756</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454683</v>
+        <v>454675</v>
       </c>
       <c r="R2" t="n">
-        <v>6991038</v>
+        <v>6991059</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113757</v>
+        <v>125113749</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454714</v>
+        <v>454596</v>
       </c>
       <c r="R3" t="n">
-        <v>6991134</v>
+        <v>6991073</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113786</v>
+        <v>125113747</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454563</v>
+        <v>454528</v>
       </c>
       <c r="R5" t="n">
-        <v>6991041</v>
+        <v>6990951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113753</v>
+        <v>125113754</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454759</v>
+        <v>454717</v>
       </c>
       <c r="R6" t="n">
-        <v>6990995</v>
+        <v>6991021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113749</v>
+        <v>125113757</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454596</v>
+        <v>454714</v>
       </c>
       <c r="R7" t="n">
-        <v>6991073</v>
+        <v>6991134</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113754</v>
+        <v>125113760</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454717</v>
+        <v>454751</v>
       </c>
       <c r="R8" t="n">
-        <v>6991021</v>
+        <v>6991130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113751</v>
+        <v>125113755</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454727</v>
+        <v>454683</v>
       </c>
       <c r="R9" t="n">
-        <v>6991007</v>
+        <v>6991038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113756</v>
+        <v>125113758</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454675</v>
+        <v>454729</v>
       </c>
       <c r="R10" t="n">
-        <v>6991059</v>
+        <v>6991137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113700</v>
+        <v>125113753</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454596</v>
+        <v>454759</v>
       </c>
       <c r="R11" t="n">
-        <v>6991038</v>
+        <v>6990995</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113758</v>
+        <v>125113786</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454729</v>
+        <v>454563</v>
       </c>
       <c r="R12" t="n">
-        <v>6991137</v>
+        <v>6991041</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1821,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113748</v>
+        <v>125113700</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454594</v>
+        <v>454596</v>
       </c>
       <c r="R13" t="n">
-        <v>6991074</v>
+        <v>6991038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,11 +1923,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113760</v>
+        <v>125113748</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454751</v>
+        <v>454594</v>
       </c>
       <c r="R14" t="n">
-        <v>6991130</v>
+        <v>6991074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113747</v>
+        <v>125113751</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454528</v>
+        <v>454727</v>
       </c>
       <c r="R15" t="n">
-        <v>6990951</v>
+        <v>6991007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113756</v>
+        <v>125113758</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454675</v>
+        <v>454729</v>
       </c>
       <c r="R2" t="n">
-        <v>6991059</v>
+        <v>6991137</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113749</v>
+        <v>125113756</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454596</v>
+        <v>454675</v>
       </c>
       <c r="R3" t="n">
-        <v>6991073</v>
+        <v>6991059</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113747</v>
+        <v>125113748</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454528</v>
+        <v>454594</v>
       </c>
       <c r="R5" t="n">
-        <v>6990951</v>
+        <v>6991074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113757</v>
+        <v>125113749</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454714</v>
+        <v>454596</v>
       </c>
       <c r="R7" t="n">
-        <v>6991134</v>
+        <v>6991073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113760</v>
+        <v>125113751</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454751</v>
+        <v>454727</v>
       </c>
       <c r="R8" t="n">
-        <v>6991130</v>
+        <v>6991007</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113755</v>
+        <v>125113700</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454683</v>
+        <v>454596</v>
       </c>
       <c r="R9" t="n">
         <v>6991038</v>
@@ -1500,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113758</v>
+        <v>125113755</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454729</v>
+        <v>454683</v>
       </c>
       <c r="R10" t="n">
-        <v>6991137</v>
+        <v>6991038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113753</v>
+        <v>125113757</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454759</v>
+        <v>454714</v>
       </c>
       <c r="R11" t="n">
-        <v>6990995</v>
+        <v>6991134</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113786</v>
+        <v>125113760</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454563</v>
+        <v>454751</v>
       </c>
       <c r="R12" t="n">
-        <v>6991041</v>
+        <v>6991130</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113700</v>
+        <v>125113747</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454596</v>
+        <v>454528</v>
       </c>
       <c r="R13" t="n">
-        <v>6991038</v>
+        <v>6990951</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113748</v>
+        <v>125113753</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454594</v>
+        <v>454759</v>
       </c>
       <c r="R14" t="n">
-        <v>6991074</v>
+        <v>6990995</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113751</v>
+        <v>125113786</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454727</v>
+        <v>454563</v>
       </c>
       <c r="R15" t="n">
-        <v>6991007</v>
+        <v>6991041</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2137,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113758</v>
+        <v>125113749</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454729</v>
+        <v>454596</v>
       </c>
       <c r="R2" t="n">
-        <v>6991137</v>
+        <v>6991073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113756</v>
+        <v>125113758</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454675</v>
+        <v>454729</v>
       </c>
       <c r="R3" t="n">
-        <v>6991059</v>
+        <v>6991137</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113750</v>
+        <v>125113700</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454597</v>
+        <v>454596</v>
       </c>
       <c r="R4" t="n">
-        <v>6991074</v>
+        <v>6991038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113748</v>
+        <v>125113751</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454594</v>
+        <v>454727</v>
       </c>
       <c r="R5" t="n">
-        <v>6991074</v>
+        <v>6991007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113754</v>
+        <v>125113747</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454717</v>
+        <v>454528</v>
       </c>
       <c r="R6" t="n">
-        <v>6991021</v>
+        <v>6990951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113749</v>
+        <v>125113755</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454596</v>
+        <v>454683</v>
       </c>
       <c r="R7" t="n">
-        <v>6991073</v>
+        <v>6991038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113751</v>
+        <v>125113748</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454727</v>
+        <v>454594</v>
       </c>
       <c r="R8" t="n">
-        <v>6991007</v>
+        <v>6991074</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113700</v>
+        <v>125113756</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454596</v>
+        <v>454675</v>
       </c>
       <c r="R9" t="n">
-        <v>6991038</v>
+        <v>6991059</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113755</v>
+        <v>125113750</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454683</v>
+        <v>454597</v>
       </c>
       <c r="R10" t="n">
-        <v>6991038</v>
+        <v>6991074</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113757</v>
+        <v>125113754</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454714</v>
+        <v>454717</v>
       </c>
       <c r="R11" t="n">
-        <v>6991134</v>
+        <v>6991021</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113760</v>
+        <v>125113757</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454751</v>
+        <v>454714</v>
       </c>
       <c r="R12" t="n">
-        <v>6991130</v>
+        <v>6991134</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113747</v>
+        <v>125113760</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454528</v>
+        <v>454751</v>
       </c>
       <c r="R13" t="n">
-        <v>6990951</v>
+        <v>6991130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113749</v>
+        <v>125113757</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454596</v>
+        <v>454714</v>
       </c>
       <c r="R2" t="n">
-        <v>6991073</v>
+        <v>6991134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113758</v>
+        <v>125113760</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454729</v>
+        <v>454751</v>
       </c>
       <c r="R3" t="n">
-        <v>6991137</v>
+        <v>6991130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113700</v>
+        <v>125113749</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,7 +932,7 @@
         <v>454596</v>
       </c>
       <c r="R4" t="n">
-        <v>6991038</v>
+        <v>6991073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113751</v>
+        <v>125113753</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454727</v>
+        <v>454759</v>
       </c>
       <c r="R5" t="n">
-        <v>6991007</v>
+        <v>6990995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113747</v>
+        <v>125113756</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454528</v>
+        <v>454675</v>
       </c>
       <c r="R6" t="n">
-        <v>6990951</v>
+        <v>6991059</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113755</v>
+        <v>125113747</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454683</v>
+        <v>454528</v>
       </c>
       <c r="R7" t="n">
-        <v>6991038</v>
+        <v>6990951</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113748</v>
+        <v>125113700</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454594</v>
+        <v>454596</v>
       </c>
       <c r="R8" t="n">
-        <v>6991074</v>
+        <v>6991038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113756</v>
+        <v>125113786</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454675</v>
+        <v>454563</v>
       </c>
       <c r="R9" t="n">
-        <v>6991059</v>
+        <v>6991041</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113750</v>
+        <v>125113751</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454597</v>
+        <v>454727</v>
       </c>
       <c r="R10" t="n">
-        <v>6991074</v>
+        <v>6991007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113754</v>
+        <v>125113758</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454717</v>
+        <v>454729</v>
       </c>
       <c r="R11" t="n">
-        <v>6991021</v>
+        <v>6991137</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113757</v>
+        <v>125113748</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454714</v>
+        <v>454594</v>
       </c>
       <c r="R12" t="n">
-        <v>6991134</v>
+        <v>6991074</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113760</v>
+        <v>125113754</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454751</v>
+        <v>454717</v>
       </c>
       <c r="R13" t="n">
-        <v>6991130</v>
+        <v>6991021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113753</v>
+        <v>125113755</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454759</v>
+        <v>454683</v>
       </c>
       <c r="R14" t="n">
-        <v>6990995</v>
+        <v>6991038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113786</v>
+        <v>125113750</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454563</v>
+        <v>454597</v>
       </c>
       <c r="R15" t="n">
-        <v>6991041</v>
+        <v>6991074</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113757</v>
+        <v>125113756</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454714</v>
+        <v>454675</v>
       </c>
       <c r="R2" t="n">
-        <v>6991134</v>
+        <v>6991059</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>125113760</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113749</v>
+        <v>125113748</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454596</v>
+        <v>454594</v>
       </c>
       <c r="R4" t="n">
-        <v>6991073</v>
+        <v>6991074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113753</v>
+        <v>125113755</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454759</v>
+        <v>454683</v>
       </c>
       <c r="R5" t="n">
-        <v>6990995</v>
+        <v>6991038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113756</v>
+        <v>125113700</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454675</v>
+        <v>454596</v>
       </c>
       <c r="R6" t="n">
-        <v>6991059</v>
+        <v>6991038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113747</v>
+        <v>125113750</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454528</v>
+        <v>454597</v>
       </c>
       <c r="R7" t="n">
-        <v>6990951</v>
+        <v>6991074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113700</v>
+        <v>125113753</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454596</v>
+        <v>454759</v>
       </c>
       <c r="R8" t="n">
-        <v>6991038</v>
+        <v>6990995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113786</v>
+        <v>125113757</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454563</v>
+        <v>454714</v>
       </c>
       <c r="R9" t="n">
-        <v>6991041</v>
+        <v>6991134</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113751</v>
+        <v>125113786</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454727</v>
+        <v>454563</v>
       </c>
       <c r="R10" t="n">
-        <v>6991007</v>
+        <v>6991041</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113758</v>
+        <v>125113749</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454729</v>
+        <v>454596</v>
       </c>
       <c r="R11" t="n">
-        <v>6991137</v>
+        <v>6991073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113748</v>
+        <v>125113758</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454594</v>
+        <v>454729</v>
       </c>
       <c r="R12" t="n">
-        <v>6991074</v>
+        <v>6991137</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113754</v>
+        <v>125113751</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454717</v>
+        <v>454727</v>
       </c>
       <c r="R13" t="n">
-        <v>6991021</v>
+        <v>6991007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113755</v>
+        <v>125113754</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454683</v>
+        <v>454717</v>
       </c>
       <c r="R14" t="n">
-        <v>6991038</v>
+        <v>6991021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113750</v>
+        <v>125113747</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454597</v>
+        <v>454528</v>
       </c>
       <c r="R15" t="n">
-        <v>6991074</v>
+        <v>6990951</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113756</v>
+        <v>125113753</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454675</v>
+        <v>454759</v>
       </c>
       <c r="R2" t="n">
-        <v>6991059</v>
+        <v>6990995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113748</v>
+        <v>125113757</v>
       </c>
       <c r="B4" t="n">
         <v>57635</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454594</v>
+        <v>454714</v>
       </c>
       <c r="R4" t="n">
-        <v>6991074</v>
+        <v>6991134</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113755</v>
+        <v>125113748</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454683</v>
+        <v>454594</v>
       </c>
       <c r="R5" t="n">
-        <v>6991038</v>
+        <v>6991074</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113750</v>
+        <v>125113749</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454597</v>
+        <v>454596</v>
       </c>
       <c r="R7" t="n">
-        <v>6991074</v>
+        <v>6991073</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113753</v>
+        <v>125113758</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454759</v>
+        <v>454729</v>
       </c>
       <c r="R8" t="n">
-        <v>6990995</v>
+        <v>6991137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113757</v>
+        <v>125113751</v>
       </c>
       <c r="B9" t="n">
         <v>57635</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454714</v>
+        <v>454727</v>
       </c>
       <c r="R9" t="n">
-        <v>6991134</v>
+        <v>6991007</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113786</v>
+        <v>125113755</v>
       </c>
       <c r="B10" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454563</v>
+        <v>454683</v>
       </c>
       <c r="R10" t="n">
-        <v>6991041</v>
+        <v>6991038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113749</v>
+        <v>125113786</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454596</v>
+        <v>454563</v>
       </c>
       <c r="R11" t="n">
-        <v>6991073</v>
+        <v>6991041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113758</v>
+        <v>125113754</v>
       </c>
       <c r="B12" t="n">
         <v>57635</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454729</v>
+        <v>454717</v>
       </c>
       <c r="R12" t="n">
-        <v>6991137</v>
+        <v>6991021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113751</v>
+        <v>125113750</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454727</v>
+        <v>454597</v>
       </c>
       <c r="R13" t="n">
-        <v>6991007</v>
+        <v>6991074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113754</v>
+        <v>125113747</v>
       </c>
       <c r="B14" t="n">
         <v>57635</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454717</v>
+        <v>454528</v>
       </c>
       <c r="R14" t="n">
-        <v>6991021</v>
+        <v>6990951</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113747</v>
+        <v>125113756</v>
       </c>
       <c r="B15" t="n">
         <v>57635</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454528</v>
+        <v>454675</v>
       </c>
       <c r="R15" t="n">
-        <v>6990951</v>
+        <v>6991059</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113750</v>
+        <v>125113747</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454597</v>
+        <v>454528</v>
       </c>
       <c r="R13" t="n">
-        <v>6991074</v>
+        <v>6990951</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113747</v>
+        <v>125113750</v>
       </c>
       <c r="B14" t="n">
         <v>57635</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454528</v>
+        <v>454597</v>
       </c>
       <c r="R14" t="n">
-        <v>6990951</v>
+        <v>6991074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113749</v>
+        <v>125113758</v>
       </c>
       <c r="B8" t="n">
         <v>57651</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454596</v>
+        <v>454729</v>
       </c>
       <c r="R8" t="n">
-        <v>6991073</v>
+        <v>6991137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113758</v>
+        <v>125113751</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454729</v>
+        <v>454727</v>
       </c>
       <c r="R9" t="n">
-        <v>6991137</v>
+        <v>6991007</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113751</v>
+        <v>125113749</v>
       </c>
       <c r="B10" t="n">
         <v>57651</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454727</v>
+        <v>454596</v>
       </c>
       <c r="R10" t="n">
-        <v>6991007</v>
+        <v>6991073</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1787,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113755</v>
+        <v>125113760</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454683</v>
+        <v>454751</v>
       </c>
       <c r="R13" t="n">
-        <v>6991038</v>
+        <v>6991130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113760</v>
+        <v>125113755</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454751</v>
+        <v>454683</v>
       </c>
       <c r="R14" t="n">
-        <v>6991130</v>
+        <v>6991038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125113756</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125113748</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125113753</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>125113750</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113758</v>
+        <v>125113749</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454729</v>
+        <v>454596</v>
       </c>
       <c r="R8" t="n">
-        <v>6991137</v>
+        <v>6991073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113751</v>
+        <v>125113758</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454727</v>
+        <v>454729</v>
       </c>
       <c r="R9" t="n">
-        <v>6991007</v>
+        <v>6991137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113749</v>
+        <v>125113751</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454596</v>
+        <v>454727</v>
       </c>
       <c r="R10" t="n">
-        <v>6991073</v>
+        <v>6991007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,7 +1586,7 @@
         <v>125113757</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>125113747</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113760</v>
+        <v>125113755</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454751</v>
+        <v>454683</v>
       </c>
       <c r="R13" t="n">
-        <v>6991130</v>
+        <v>6991038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113755</v>
+        <v>125113760</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454683</v>
+        <v>454751</v>
       </c>
       <c r="R14" t="n">
-        <v>6991038</v>
+        <v>6991130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +1994,7 @@
         <v>125113754</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -1787,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113755</v>
+        <v>125113760</v>
       </c>
       <c r="B13" t="n">
         <v>57652</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454683</v>
+        <v>454751</v>
       </c>
       <c r="R13" t="n">
-        <v>6991038</v>
+        <v>6991130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113760</v>
+        <v>125113755</v>
       </c>
       <c r="B14" t="n">
         <v>57652</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454751</v>
+        <v>454683</v>
       </c>
       <c r="R14" t="n">
-        <v>6991130</v>
+        <v>6991038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125113756</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125113748</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125113753</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>125113750</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>125113749</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>125113758</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>125113751</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>125113757</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>125113747</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113760</v>
+        <v>125113755</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454751</v>
+        <v>454683</v>
       </c>
       <c r="R13" t="n">
-        <v>6991130</v>
+        <v>6991038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113755</v>
+        <v>125113760</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454683</v>
+        <v>454751</v>
       </c>
       <c r="R14" t="n">
-        <v>6991038</v>
+        <v>6991130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +1994,7 @@
         <v>125113754</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125113756</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125113748</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>125113753</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>125113750</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>125113749</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>125113758</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>125113751</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>125113757</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>125113747</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>125113755</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>125113760</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>125113754</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 12995-2024 artfynd.xlsx
+++ b/artfynd/A 12995-2024 artfynd.xlsx
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113749</v>
+        <v>125113758</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454596</v>
+        <v>454729</v>
       </c>
       <c r="R8" t="n">
-        <v>6991073</v>
+        <v>6991137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113758</v>
+        <v>125113749</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454729</v>
+        <v>454596</v>
       </c>
       <c r="R9" t="n">
-        <v>6991137</v>
+        <v>6991073</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1787,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113755</v>
+        <v>125113760</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454683</v>
+        <v>454751</v>
       </c>
       <c r="R13" t="n">
-        <v>6991038</v>
+        <v>6991130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113760</v>
+        <v>125113755</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454751</v>
+        <v>454683</v>
       </c>
       <c r="R14" t="n">
-        <v>6991130</v>
+        <v>6991038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
